--- a/Excel/玩家.xlsx
+++ b/Excel/玩家.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MyProjects\SpectraAbyss\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C94233-C2E9-4560-BA48-22E0B81F1C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="25600" windowHeight="10270"/>
   </bookViews>
   <sheets>
     <sheet name="Player" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -28,137 +30,432 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
   <si>
     <t>控制器</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>转生等级</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>阶段</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>双索引</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>最大阶段</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>转生任务阶段
-1：对话任务
-2：转生点收集任务
-3：BOSS任务
-4：星盘小游戏</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>转生任务阶段 1:对话任务 2:转生点收集任务 3:BOSS任务 4:星盘小游戏</t>
   </si>
   <si>
     <t>阶段icon</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>转生开启等级</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>导出开关</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>字段</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Lv</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Stage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Index</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>MaxStage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>StageDiff</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Stageicon</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>StartLv</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>数据类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
   </si>
   <si>
     <t>hbs1/hbs1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO</t>
   </si>
   <si>
     <t>END</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>NO</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Number</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>String</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -166,9 +463,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -179,17 +718,61 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -238,7 +821,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -273,7 +856,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -447,32 +1030,27 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="10.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.8333333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1"/>
     <col min="4" max="4" width="11.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.75" style="1" customWidth="1"/>
     <col min="6" max="6" width="21" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.08203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.0833333333333" style="1" customWidth="1"/>
     <col min="8" max="8" width="26.5" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" ht="105" customHeight="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +1076,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -524,7 +1102,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -550,33 +1128,33 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" ht="21.75" customHeight="1" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>0</v>
       </c>
@@ -587,7 +1165,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="str">
-        <f t="shared" ref="D5:D7" si="0">B5&amp;"_"&amp;C5</f>
+        <f t="shared" ref="D5:D8" si="0">B5&amp;"_"&amp;C5</f>
         <v>1_1</v>
       </c>
       <c r="E5" s="1">
@@ -603,7 +1181,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>0</v>
       </c>
@@ -630,7 +1208,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>0</v>
       </c>
@@ -657,7 +1235,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>0</v>
       </c>
@@ -668,7 +1246,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="1" t="str">
-        <f>B8&amp;"_"&amp;C8</f>
+        <f t="shared" si="0"/>
         <v>1_4</v>
       </c>
       <c r="E8" s="1">
@@ -678,13 +1256,13 @@
         <v>2</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H8" s="1">
         <v>421</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>0</v>
       </c>
@@ -695,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="1" t="str">
-        <f t="shared" ref="D9:D10" si="1">B9&amp;"_"&amp;C9</f>
+        <f t="shared" ref="D9:D11" si="1">B9&amp;"_"&amp;C9</f>
         <v>1_5</v>
       </c>
       <c r="E9" s="1">
@@ -705,13 +1283,13 @@
         <v>2</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H9" s="1">
         <v>461</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>0</v>
       </c>
@@ -738,7 +1316,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>0</v>
       </c>
@@ -749,7 +1327,7 @@
         <v>7</v>
       </c>
       <c r="D11" s="1" t="str">
-        <f>B11&amp;"_"&amp;C11</f>
+        <f t="shared" si="1"/>
         <v>1_7</v>
       </c>
       <c r="E11" s="1">
@@ -765,7 +1343,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>0</v>
       </c>
@@ -776,7 +1354,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="str">
-        <f t="shared" ref="D12:D13" si="2">B12&amp;"_"&amp;C12</f>
+        <f t="shared" ref="D12:D14" si="2">B12&amp;"_"&amp;C12</f>
         <v>2_1</v>
       </c>
       <c r="E12" s="1">
@@ -792,7 +1370,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>0</v>
       </c>
@@ -819,7 +1397,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <v>0</v>
       </c>
@@ -830,7 +1408,7 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="str">
-        <f>B14&amp;"_"&amp;C14</f>
+        <f t="shared" si="2"/>
         <v>2_3</v>
       </c>
       <c r="E14" s="1">
@@ -840,13 +1418,13 @@
         <v>2</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H14" s="1">
         <v>941</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>0</v>
       </c>
@@ -857,7 +1435,7 @@
         <v>4</v>
       </c>
       <c r="D15" s="1" t="str">
-        <f t="shared" ref="D15:D16" si="3">B15&amp;"_"&amp;C15</f>
+        <f t="shared" ref="D15:D17" si="3">B15&amp;"_"&amp;C15</f>
         <v>2_4</v>
       </c>
       <c r="E15" s="1">
@@ -867,13 +1445,13 @@
         <v>2</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H15" s="1">
         <v>971</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>0</v>
       </c>
@@ -900,7 +1478,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8">
       <c r="A17" s="1">
         <v>0</v>
       </c>
@@ -911,7 +1489,7 @@
         <v>6</v>
       </c>
       <c r="D17" s="1" t="str">
-        <f>B17&amp;"_"&amp;C17</f>
+        <f t="shared" si="3"/>
         <v>2_6</v>
       </c>
       <c r="E17" s="1">
@@ -927,7 +1505,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8">
       <c r="A18" s="1">
         <v>0</v>
       </c>
@@ -938,7 +1516,7 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="str">
-        <f t="shared" ref="D18:D19" si="4">B18&amp;"_"&amp;C18</f>
+        <f t="shared" ref="D18:D20" si="4">B18&amp;"_"&amp;C18</f>
         <v>3_1</v>
       </c>
       <c r="E18" s="1">
@@ -954,7 +1532,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <v>0</v>
       </c>
@@ -981,7 +1559,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>0</v>
       </c>
@@ -992,7 +1570,7 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="str">
-        <f>B20&amp;"_"&amp;C20</f>
+        <f t="shared" si="4"/>
         <v>3_3</v>
       </c>
       <c r="E20" s="1">
@@ -1002,13 +1580,13 @@
         <v>2</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H20" s="1">
         <v>1431</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <v>0</v>
       </c>
@@ -1019,7 +1597,7 @@
         <v>4</v>
       </c>
       <c r="D21" s="1" t="str">
-        <f t="shared" ref="D21:D22" si="5">B21&amp;"_"&amp;C21</f>
+        <f t="shared" ref="D21:D23" si="5">B21&amp;"_"&amp;C21</f>
         <v>3_4</v>
       </c>
       <c r="E21" s="1">
@@ -1029,13 +1607,13 @@
         <v>2</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H21" s="1">
         <v>1481</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8">
       <c r="A22" s="1">
         <v>0</v>
       </c>
@@ -1062,7 +1640,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8">
       <c r="A23" s="1">
         <v>0</v>
       </c>
@@ -1073,7 +1651,7 @@
         <v>6</v>
       </c>
       <c r="D23" s="1" t="str">
-        <f>B23&amp;"_"&amp;C23</f>
+        <f t="shared" si="5"/>
         <v>3_6</v>
       </c>
       <c r="E23" s="1">
@@ -1089,7 +1667,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8">
       <c r="A24" s="1">
         <v>0</v>
       </c>
@@ -1100,7 +1678,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="1" t="str">
-        <f t="shared" ref="D24:D25" si="6">B24&amp;"_"&amp;C24</f>
+        <f t="shared" ref="D24:D26" si="6">B24&amp;"_"&amp;C24</f>
         <v>4_1</v>
       </c>
       <c r="E24" s="1">
@@ -1116,7 +1694,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8">
       <c r="A25" s="1">
         <v>0</v>
       </c>
@@ -1143,7 +1721,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8">
       <c r="A26" s="1">
         <v>0</v>
       </c>
@@ -1154,7 +1732,7 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="str">
-        <f>B26&amp;"_"&amp;C26</f>
+        <f t="shared" si="6"/>
         <v>4_3</v>
       </c>
       <c r="E26" s="1">
@@ -1164,13 +1742,13 @@
         <v>2</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H26" s="1">
         <v>1921</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8">
       <c r="A27" s="1">
         <v>0</v>
       </c>
@@ -1181,7 +1759,7 @@
         <v>4</v>
       </c>
       <c r="D27" s="1" t="str">
-        <f t="shared" ref="D27" si="7">B27&amp;"_"&amp;C27</f>
+        <f t="shared" ref="D27:D29" si="7">B27&amp;"_"&amp;C27</f>
         <v>4_4</v>
       </c>
       <c r="E27" s="1">
@@ -1191,13 +1769,13 @@
         <v>2</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H27" s="1">
         <v>1971</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8">
       <c r="A28" s="1">
         <v>0</v>
       </c>
@@ -1208,7 +1786,7 @@
         <v>5</v>
       </c>
       <c r="D28" s="1" t="str">
-        <f>B28&amp;"_"&amp;C28</f>
+        <f t="shared" si="7"/>
         <v>4_5</v>
       </c>
       <c r="E28" s="1">
@@ -1224,7 +1802,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8">
       <c r="A29" s="1">
         <v>0</v>
       </c>
@@ -1235,7 +1813,7 @@
         <v>6</v>
       </c>
       <c r="D29" s="1" t="str">
-        <f>B29&amp;"_"&amp;C29</f>
+        <f t="shared" si="7"/>
         <v>4_6</v>
       </c>
       <c r="E29" s="1">
@@ -1251,9 +1829,9 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B30" s="1">
         <v>3</v>
@@ -1272,15 +1850,15 @@
         <v>2</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H30" s="1">
         <v>1500</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B31" s="1">
         <v>3</v>
@@ -1299,15 +1877,15 @@
         <v>2</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H31" s="1">
         <v>1500</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B32" s="1">
         <v>3</v>
@@ -1332,9 +1910,9 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B33" s="1">
         <v>3</v>
@@ -1359,9 +1937,9 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B34" s="1">
         <v>4</v>
@@ -1380,15 +1958,15 @@
         <v>2</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H34" s="1">
         <v>1500</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B35" s="1">
         <v>4</v>
@@ -1407,15 +1985,15 @@
         <v>2</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H35" s="1">
         <v>1500</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B36" s="1">
         <v>4</v>
@@ -1440,9 +2018,9 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B37" s="1">
         <v>4</v>
@@ -1467,7 +2045,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8">
       <c r="A38" s="1">
         <v>0</v>
       </c>
@@ -1488,13 +2066,13 @@
         <v>2</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H38" s="1">
         <v>1500</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8">
       <c r="A39" s="1">
         <v>0</v>
       </c>
@@ -1515,15 +2093,15 @@
         <v>2</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H39" s="1">
         <v>1500</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B40" s="1">
         <v>5</v>
@@ -1549,7 +2127,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>